--- a/data/trans_orig/IQ2605_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IQ2605_R-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si hacen uso de la sombra para evitar el sol en 2007 (tasa de respuesta: 100,0%)</t>
+          <t>Menores según si el verano pasado hicieron uso de la sombra para evitar el sol en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>14360</t>
+          <t>14668</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>27530</t>
+          <t>27933</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>20,54%</t>
+          <t>20,84%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>16116</t>
+          <t>16268</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>30407</t>
+          <t>30756</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,57%</t>
+          <t>20,81%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>34150</t>
+          <t>34266</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>53790</t>
+          <t>53768</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>19,08%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>36135</t>
+          <t>36455</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>54671</t>
+          <t>53144</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>26,96%</t>
+          <t>27,2%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>40,8%</t>
+          <t>39,66%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>31284</t>
+          <t>30770</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>48281</t>
+          <t>46728</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>21,16%</t>
+          <t>20,82%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>32,66%</t>
+          <t>31,61%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>72465</t>
+          <t>71322</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>97274</t>
+          <t>95831</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>25,71%</t>
+          <t>25,31%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>34,51%</t>
+          <t>34,0%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>49163</t>
+          <t>48960</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>68412</t>
+          <t>67450</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>36,69%</t>
+          <t>36,53%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>51,05%</t>
+          <t>50,33%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>62767</t>
+          <t>62485</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>82143</t>
+          <t>81518</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>42,46%</t>
+          <t>42,27%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>55,57%</t>
+          <t>55,15%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>117588</t>
+          <t>116885</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>144767</t>
+          <t>145651</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>41,72%</t>
+          <t>41,47%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>51,37%</t>
+          <t>51,68%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3392</t>
+          <t>3052</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11988</t>
+          <t>11710</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2975</t>
+          <t>2626</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10335</t>
+          <t>10373</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7436</t>
+          <t>7538</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>18844</t>
+          <t>18357</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,51%</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1227</t>
+          <t>1349</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>7706</t>
+          <t>7346</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1200,12 +1200,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>4595</t>
+          <t>4815</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>14231</t>
+          <t>14132</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1235,12 +1235,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>7132</t>
+          <t>7168</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>17646</t>
+          <t>18154</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,44%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>28988</t>
+          <t>29281</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>45731</t>
+          <t>45857</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>15,2%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>23,73%</t>
+          <t>23,8%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>41652</t>
+          <t>41022</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>60640</t>
+          <t>61273</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19,87%</t>
+          <t>19,57%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>28,93%</t>
+          <t>29,23%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>73780</t>
+          <t>73893</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>101321</t>
+          <t>99876</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>18,37%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>25,19%</t>
+          <t>24,83%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>54219</t>
+          <t>52531</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>73864</t>
+          <t>73079</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>28,14%</t>
+          <t>27,26%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>38,33%</t>
+          <t>37,93%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>60032</t>
+          <t>58862</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>80941</t>
+          <t>81380</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>28,64%</t>
+          <t>28,08%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>38,62%</t>
+          <t>38,83%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>119326</t>
+          <t>118109</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>147967</t>
+          <t>147890</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>29,66%</t>
+          <t>29,36%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>36,78%</t>
+          <t>36,76%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>65139</t>
+          <t>66422</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>86463</t>
+          <t>87181</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>33,81%</t>
+          <t>34,47%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>44,87%</t>
+          <t>45,24%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>59662</t>
+          <t>59001</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>81086</t>
+          <t>81393</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>28,46%</t>
+          <t>28,15%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>38,69%</t>
+          <t>38,83%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>131668</t>
+          <t>131250</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>161477</t>
+          <t>162170</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>32,73%</t>
+          <t>32,63%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>40,14%</t>
+          <t>40,31%</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5274</t>
+          <t>4628</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14788</t>
+          <t>14427</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3957</t>
+          <t>3914</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>12379</t>
+          <t>13058</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>11612</t>
+          <t>11545</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>24291</t>
+          <t>24509</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,09%</t>
         </is>
       </c>
     </row>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3949</t>
+          <t>4291</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>12659</t>
+          <t>12164</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1882,12 +1882,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,12 +1902,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>6173</t>
+          <t>6190</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>16504</t>
+          <t>17112</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1917,12 +1917,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>13110</t>
+          <t>12606</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>26632</t>
+          <t>25936</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1952,12 +1952,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,45%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>20398</t>
+          <t>21218</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>35263</t>
+          <t>35212</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>16,12%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>26,79%</t>
+          <t>26,75%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>24158</t>
+          <t>24620</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>40187</t>
+          <t>39246</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>17,25%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>28,16%</t>
+          <t>27,5%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>48801</t>
+          <t>48626</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>69329</t>
+          <t>69394</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>17,72%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>25,27%</t>
+          <t>25,29%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>32583</t>
+          <t>32511</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>48062</t>
+          <t>47799</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>24,76%</t>
+          <t>24,7%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>36,52%</t>
+          <t>36,32%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>26405</t>
+          <t>26016</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>42161</t>
+          <t>41933</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>29,54%</t>
+          <t>29,38%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>62850</t>
+          <t>62640</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>85286</t>
+          <t>85512</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>22,91%</t>
+          <t>22,83%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>31,09%</t>
+          <t>31,17%</t>
         </is>
       </c>
     </row>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>41528</t>
+          <t>41418</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>57380</t>
+          <t>57969</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>31,55%</t>
+          <t>31,47%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>43,6%</t>
+          <t>44,04%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>48522</t>
+          <t>48880</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>66490</t>
+          <t>67327</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>33,99%</t>
+          <t>34,25%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>46,58%</t>
+          <t>47,17%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>94958</t>
+          <t>94699</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>121794</t>
+          <t>119903</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2408,12 +2408,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>34,61%</t>
+          <t>34,52%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>44,39%</t>
+          <t>43,7%</t>
         </is>
       </c>
     </row>
@@ -2436,12 +2436,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4175</t>
+          <t>4203</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12405</t>
+          <t>12456</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2451,12 +2451,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2471,12 +2471,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>9082</t>
+          <t>8971</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>20154</t>
+          <t>20896</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2486,12 +2486,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>15268</t>
+          <t>15556</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>30137</t>
+          <t>29619</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>10,8%</t>
         </is>
       </c>
     </row>
@@ -2549,12 +2549,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3788</t>
+          <t>3818</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>12217</t>
+          <t>12332</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2564,12 +2564,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,12 +2584,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2568</t>
+          <t>2733</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>10233</t>
+          <t>10260</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2599,12 +2599,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,12 +2619,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>7714</t>
+          <t>8139</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>18663</t>
+          <t>19319</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2634,12 +2634,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>7,04%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>52156</t>
+          <t>51832</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>73590</t>
+          <t>73601</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>25,28%</t>
+          <t>25,12%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>35,66%</t>
+          <t>35,67%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>54942</t>
+          <t>53388</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>76268</t>
+          <t>75301</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>26,61%</t>
+          <t>25,86%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>36,94%</t>
+          <t>36,47%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>112325</t>
+          <t>112319</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>144105</t>
+          <t>142235</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2869,7 +2869,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>34,91%</t>
+          <t>34,45%</t>
         </is>
       </c>
     </row>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>52623</t>
+          <t>53022</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>76757</t>
+          <t>75448</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2907,12 +2907,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>25,5%</t>
+          <t>25,7%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>37,2%</t>
+          <t>36,56%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2927,12 +2927,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>50655</t>
+          <t>51821</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>71611</t>
+          <t>72187</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2942,12 +2942,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>24,53%</t>
+          <t>25,1%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>34,68%</t>
+          <t>34,96%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>109336</t>
+          <t>108734</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>139545</t>
+          <t>140282</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2977,12 +2977,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>26,49%</t>
+          <t>26,34%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>33,8%</t>
+          <t>33,98%</t>
         </is>
       </c>
     </row>
@@ -3005,12 +3005,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>54759</t>
+          <t>53730</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>76542</t>
+          <t>77198</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3020,12 +3020,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>26,54%</t>
+          <t>26,04%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>37,09%</t>
+          <t>37,41%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>51585</t>
+          <t>50035</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>73052</t>
+          <t>70727</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>24,98%</t>
+          <t>24,23%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>35,38%</t>
+          <t>34,26%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,12 +3075,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>111567</t>
+          <t>111947</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>143469</t>
+          <t>143739</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>27,03%</t>
+          <t>27,12%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>34,75%</t>
+          <t>34,82%</t>
         </is>
       </c>
     </row>
@@ -3118,12 +3118,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3503</t>
+          <t>3258</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>12273</t>
+          <t>12170</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3133,12 +3133,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,12 +3153,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>7847</t>
+          <t>7998</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>19331</t>
+          <t>20286</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>13759</t>
+          <t>13254</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>28222</t>
+          <t>27732</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,72%</t>
         </is>
       </c>
     </row>
@@ -3231,12 +3231,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3654</t>
+          <t>3707</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>12994</t>
+          <t>13362</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3246,12 +3246,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,12 +3266,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2754</t>
+          <t>2783</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>10800</t>
+          <t>11137</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>8562</t>
+          <t>8178</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>20366</t>
+          <t>20754</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>5,03%</t>
         </is>
       </c>
     </row>
@@ -3461,12 +3461,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>129814</t>
+          <t>128779</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>164474</t>
+          <t>163087</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3476,12 +3476,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>19,38%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>24,75%</t>
+          <t>24,54%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>153580</t>
+          <t>150294</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>189734</t>
+          <t>188756</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3511,12 +3511,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>21,27%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>26,85%</t>
+          <t>26,71%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>290026</t>
+          <t>293204</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>340761</t>
+          <t>341896</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
+          <t>21,38%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>24,85%</t>
+          <t>24,93%</t>
         </is>
       </c>
     </row>
@@ -3574,12 +3574,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>192111</t>
+          <t>192218</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>232941</t>
+          <t>232820</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3589,12 +3589,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>28,9%</t>
+          <t>28,92%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>35,05%</t>
+          <t>35,03%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3609,12 +3609,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>184502</t>
+          <t>184486</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>222244</t>
+          <t>222935</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3629,7 +3629,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>31,45%</t>
+          <t>31,55%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3644,12 +3644,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>387725</t>
+          <t>387796</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>441737</t>
+          <t>442687</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3659,12 +3659,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>28,27%</t>
+          <t>28,28%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>32,21%</t>
+          <t>32,28%</t>
         </is>
       </c>
     </row>
@@ -3687,12 +3687,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>229279</t>
+          <t>228681</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>270982</t>
+          <t>270905</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3702,12 +3702,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>34,5%</t>
+          <t>34,41%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>40,77%</t>
+          <t>40,76%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3722,12 +3722,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>242833</t>
+          <t>241221</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>281982</t>
+          <t>283467</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3737,12 +3737,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>34,37%</t>
+          <t>34,14%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>39,91%</t>
+          <t>40,12%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3757,12 +3757,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>484331</t>
+          <t>484525</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>543507</t>
+          <t>543345</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3772,12 +3772,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>35,32%</t>
+          <t>35,33%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>39,63%</t>
+          <t>39,62%</t>
         </is>
       </c>
     </row>
@@ -3800,12 +3800,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>22649</t>
+          <t>22382</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>40171</t>
+          <t>39697</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3815,12 +3815,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3835,12 +3835,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>32728</t>
+          <t>31481</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>51148</t>
+          <t>51701</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3850,12 +3850,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3870,12 +3870,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>59937</t>
+          <t>58201</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>85529</t>
+          <t>85068</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3885,12 +3885,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,2%</t>
         </is>
       </c>
     </row>
@@ -3913,12 +3913,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>18539</t>
+          <t>18228</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>34209</t>
+          <t>34262</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3928,7 +3928,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>22650</t>
+          <t>22773</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>40357</t>
+          <t>40336</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3963,7 +3963,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -3983,12 +3983,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>44124</t>
+          <t>45881</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>67615</t>
+          <t>69145</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3998,12 +3998,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>5,04%</t>
         </is>
       </c>
     </row>
@@ -4180,7 +4180,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si hacen uso de la sombra para evitar el sol en 2012 (tasa de respuesta: 99,66%)</t>
+          <t>Menores según si el verano pasado hicieron uso de la sombra para evitar el sol en 2012 (tasa de respuesta: 99,66%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4375,12 +4375,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>42226</t>
+          <t>43268</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>62711</t>
+          <t>62271</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4390,12 +4390,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>30,6%</t>
+          <t>31,35%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>45,44%</t>
+          <t>45,13%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>50810</t>
+          <t>50292</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>70503</t>
+          <t>70207</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4425,12 +4425,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>34,33%</t>
+          <t>33,98%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>47,63%</t>
+          <t>47,43%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>98572</t>
+          <t>97017</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>127390</t>
+          <t>124711</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4460,12 +4460,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>34,47%</t>
+          <t>33,92%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>44,54%</t>
+          <t>43,6%</t>
         </is>
       </c>
     </row>
@@ -4488,12 +4488,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>46785</t>
+          <t>47392</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>66986</t>
+          <t>66497</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4503,12 +4503,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>33,9%</t>
+          <t>34,34%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>48,54%</t>
+          <t>48,19%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4523,12 +4523,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>45408</t>
+          <t>45273</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>64585</t>
+          <t>65501</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4538,12 +4538,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>30,68%</t>
+          <t>30,59%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>43,64%</t>
+          <t>44,26%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4558,12 +4558,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>98494</t>
+          <t>97974</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>125544</t>
+          <t>126263</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4573,12 +4573,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>34,44%</t>
+          <t>34,26%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>43,9%</t>
+          <t>44,15%</t>
         </is>
       </c>
     </row>
@@ -4601,12 +4601,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>16825</t>
+          <t>17581</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>32647</t>
+          <t>33324</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4616,12 +4616,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>23,66%</t>
+          <t>24,15%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4636,12 +4636,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>15355</t>
+          <t>15659</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>30588</t>
+          <t>31142</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>21,04%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4671,12 +4671,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>36454</t>
+          <t>35769</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>57310</t>
+          <t>58099</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4686,12 +4686,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>20,31%</t>
         </is>
       </c>
     </row>
@@ -4719,7 +4719,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3701</t>
+          <t>5249</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4734,7 +4734,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4749,12 +4749,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1952</t>
+          <t>1510</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8872</t>
+          <t>9320</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4764,12 +4764,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4784,12 +4784,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2080</t>
+          <t>2045</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>9855</t>
+          <t>9570</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4799,12 +4799,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,35%</t>
         </is>
       </c>
     </row>
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1336</t>
+          <t>1331</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>7839</t>
+          <t>8692</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4842,12 +4842,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4862,12 +4862,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>3418</t>
+          <t>3236</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>12388</t>
+          <t>12313</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4877,12 +4877,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4897,12 +4897,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>5912</t>
+          <t>5848</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>17691</t>
+          <t>17682</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4912,12 +4912,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,18%</t>
         </is>
       </c>
     </row>
@@ -5057,7 +5057,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>72696</t>
+          <t>71907</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -5072,7 +5072,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>36,69%</t>
+          <t>36,29%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -5092,12 +5092,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>70359</t>
+          <t>69517</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>95461</t>
+          <t>93363</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5107,12 +5107,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>32,42%</t>
+          <t>32,03%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>43,98%</t>
+          <t>43,01%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5127,12 +5127,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>148313</t>
+          <t>148854</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>181711</t>
+          <t>180676</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5142,12 +5142,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>35,72%</t>
+          <t>35,85%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>43,76%</t>
+          <t>43,51%</t>
         </is>
       </c>
     </row>
@@ -5170,12 +5170,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>63891</t>
+          <t>63476</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>84929</t>
+          <t>85723</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5185,12 +5185,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>32,24%</t>
+          <t>32,03%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>42,86%</t>
+          <t>43,26%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5205,12 +5205,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>74931</t>
+          <t>75199</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>98771</t>
+          <t>98095</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5220,12 +5220,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>34,52%</t>
+          <t>34,65%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>45,51%</t>
+          <t>45,2%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5240,12 +5240,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>144925</t>
+          <t>144807</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>177887</t>
+          <t>176773</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5255,12 +5255,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>34,9%</t>
+          <t>34,88%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>42,84%</t>
+          <t>42,57%</t>
         </is>
       </c>
     </row>
@@ -5283,12 +5283,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>23234</t>
+          <t>22992</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>38438</t>
+          <t>38823</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5298,12 +5298,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>19,59%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5318,12 +5318,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>28052</t>
+          <t>27388</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>45637</t>
+          <t>45617</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5333,12 +5333,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>21,02%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5353,12 +5353,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>55192</t>
+          <t>55920</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>78445</t>
+          <t>79073</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5368,12 +5368,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>19,04%</t>
         </is>
       </c>
     </row>
@@ -5396,12 +5396,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1364</t>
+          <t>1874</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8453</t>
+          <t>9545</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5411,12 +5411,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5431,12 +5431,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>618</t>
+          <t>654</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5843</t>
+          <t>6495</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5446,12 +5446,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5466,12 +5466,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3333</t>
+          <t>3204</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>11963</t>
+          <t>11587</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5481,12 +5481,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,79%</t>
         </is>
       </c>
     </row>
@@ -5509,12 +5509,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3554</t>
+          <t>3602</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>11531</t>
+          <t>11094</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5524,12 +5524,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5544,12 +5544,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>5401</t>
+          <t>5464</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>15537</t>
+          <t>15275</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5559,12 +5559,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5579,12 +5579,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>10601</t>
+          <t>10989</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>22982</t>
+          <t>23582</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5594,12 +5594,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,68%</t>
         </is>
       </c>
     </row>
@@ -5739,12 +5739,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>52584</t>
+          <t>51622</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>71265</t>
+          <t>70665</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5754,12 +5754,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>35,09%</t>
+          <t>34,44%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>47,55%</t>
+          <t>47,15%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5774,12 +5774,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>52308</t>
+          <t>52294</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>72447</t>
+          <t>71944</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5789,12 +5789,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>33,02%</t>
+          <t>33,01%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>45,73%</t>
+          <t>45,42%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5809,12 +5809,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>108020</t>
+          <t>108941</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>136546</t>
+          <t>136476</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5824,12 +5824,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>35,04%</t>
+          <t>35,34%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>44,29%</t>
+          <t>44,27%</t>
         </is>
       </c>
     </row>
@@ -5852,12 +5852,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>34648</t>
+          <t>34281</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>50675</t>
+          <t>51562</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5867,12 +5867,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>23,12%</t>
+          <t>22,87%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>33,81%</t>
+          <t>34,4%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5887,12 +5887,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>43456</t>
+          <t>44067</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>61459</t>
+          <t>63362</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5902,12 +5902,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>27,43%</t>
+          <t>27,82%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>38,8%</t>
+          <t>40,0%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5922,12 +5922,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>83753</t>
+          <t>83432</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>108851</t>
+          <t>108727</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5937,12 +5937,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>27,17%</t>
+          <t>27,06%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>35,31%</t>
+          <t>35,27%</t>
         </is>
       </c>
     </row>
@@ -5965,12 +5965,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>26937</t>
+          <t>26403</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>43727</t>
+          <t>43065</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5980,12 +5980,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>29,18%</t>
+          <t>28,74%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6000,12 +6000,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>22130</t>
+          <t>21857</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>37779</t>
+          <t>37645</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6015,12 +6015,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>23,85%</t>
+          <t>23,76%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6035,12 +6035,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>52909</t>
+          <t>54041</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>75890</t>
+          <t>76169</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>17,53%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>24,62%</t>
+          <t>24,71%</t>
         </is>
       </c>
     </row>
@@ -6078,12 +6078,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1289</t>
+          <t>1339</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7559</t>
+          <t>8366</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6093,12 +6093,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6113,12 +6113,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3553</t>
+          <t>3600</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>12574</t>
+          <t>13118</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>6368</t>
+          <t>6019</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>17528</t>
+          <t>16882</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,48%</t>
         </is>
       </c>
     </row>
@@ -6191,12 +6191,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>4844</t>
+          <t>4776</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>14484</t>
+          <t>13669</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6206,12 +6206,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>3685</t>
+          <t>4039</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>11832</t>
+          <t>12050</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>10491</t>
+          <t>10437</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>22838</t>
+          <t>23056</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,48%</t>
         </is>
       </c>
     </row>
@@ -6421,12 +6421,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>62629</t>
+          <t>63187</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>86331</t>
+          <t>86469</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6436,12 +6436,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>31,03%</t>
+          <t>31,3%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>42,77%</t>
+          <t>42,84%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>49071</t>
+          <t>49123</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>70126</t>
+          <t>70608</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>24,38%</t>
+          <t>24,4%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>34,84%</t>
+          <t>35,08%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6491,12 +6491,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>116490</t>
+          <t>117461</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>150066</t>
+          <t>149753</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6506,12 +6506,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>28,89%</t>
+          <t>29,14%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>37,22%</t>
+          <t>37,15%</t>
         </is>
       </c>
     </row>
@@ -6534,12 +6534,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>52538</t>
+          <t>51531</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>74740</t>
+          <t>75496</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6549,12 +6549,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>26,03%</t>
+          <t>25,53%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>37,03%</t>
+          <t>37,4%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6569,12 +6569,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>61214</t>
+          <t>62110</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>83973</t>
+          <t>85556</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6584,12 +6584,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>30,41%</t>
+          <t>30,85%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>41,71%</t>
+          <t>42,5%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6604,12 +6604,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>121811</t>
+          <t>121376</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>154602</t>
+          <t>154087</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6619,12 +6619,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>30,21%</t>
+          <t>30,11%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>38,35%</t>
+          <t>38,22%</t>
         </is>
       </c>
     </row>
@@ -6647,12 +6647,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>36751</t>
+          <t>36469</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>57474</t>
+          <t>57312</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6662,12 +6662,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>18,07%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>28,47%</t>
+          <t>28,39%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6682,12 +6682,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>39666</t>
+          <t>39941</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>59898</t>
+          <t>60106</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6697,12 +6697,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>19,7%</t>
+          <t>19,84%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>29,75%</t>
+          <t>29,86%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6717,12 +6717,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>81302</t>
+          <t>81860</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>110496</t>
+          <t>110240</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6732,12 +6732,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>20,17%</t>
+          <t>20,31%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>27,41%</t>
+          <t>27,34%</t>
         </is>
       </c>
     </row>
@@ -6760,12 +6760,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>6034</t>
+          <t>5788</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>16276</t>
+          <t>17013</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6775,12 +6775,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6795,12 +6795,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2691</t>
+          <t>2668</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>10366</t>
+          <t>10351</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6810,12 +6810,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6830,12 +6830,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>9760</t>
+          <t>9623</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>23218</t>
+          <t>23095</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6845,12 +6845,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,73%</t>
         </is>
       </c>
     </row>
@@ -6873,12 +6873,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>4461</t>
+          <t>4471</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>14635</t>
+          <t>15506</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6893,7 +6893,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6908,12 +6908,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>8554</t>
+          <t>7824</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>20830</t>
+          <t>21182</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6923,12 +6923,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6943,12 +6943,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>14609</t>
+          <t>15094</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>30770</t>
+          <t>32155</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6958,12 +6958,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,98%</t>
         </is>
       </c>
     </row>
@@ -7103,12 +7103,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>248148</t>
+          <t>249399</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>288307</t>
+          <t>292892</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7118,12 +7118,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>36,07%</t>
+          <t>36,26%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>41,91%</t>
+          <t>42,58%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>240824</t>
+          <t>239807</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>284837</t>
+          <t>285405</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7153,12 +7153,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>33,23%</t>
+          <t>33,09%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>39,3%</t>
+          <t>39,38%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>500460</t>
+          <t>503087</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>561893</t>
+          <t>562617</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7188,12 +7188,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>35,43%</t>
+          <t>35,61%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>39,78%</t>
+          <t>39,83%</t>
         </is>
       </c>
     </row>
@@ -7216,12 +7216,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>216803</t>
+          <t>216620</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>257248</t>
+          <t>257393</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7231,12 +7231,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>31,52%</t>
+          <t>31,49%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>37,4%</t>
+          <t>37,42%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7251,12 +7251,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>246004</t>
+          <t>247673</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>289936</t>
+          <t>291858</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7266,12 +7266,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>33,94%</t>
+          <t>34,17%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>40,0%</t>
+          <t>40,27%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>471161</t>
+          <t>473190</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>534043</t>
+          <t>533764</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7301,12 +7301,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>33,35%</t>
+          <t>33,5%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>37,8%</t>
+          <t>37,78%</t>
         </is>
       </c>
     </row>
@@ -7329,12 +7329,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>119133</t>
+          <t>117337</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>153827</t>
+          <t>153101</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7344,12 +7344,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>22,36%</t>
+          <t>22,26%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7364,12 +7364,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>120420</t>
+          <t>119918</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>155470</t>
+          <t>154940</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7379,12 +7379,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>16,55%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>21,45%</t>
+          <t>21,38%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7399,12 +7399,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>250425</t>
+          <t>249670</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>298128</t>
+          <t>300277</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>17,67%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>21,1%</t>
+          <t>21,26%</t>
         </is>
       </c>
     </row>
@@ -7442,12 +7442,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>12432</t>
+          <t>12171</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>27323</t>
+          <t>26693</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7457,12 +7457,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7477,12 +7477,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>13481</t>
+          <t>13316</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>28046</t>
+          <t>27337</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7492,12 +7492,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7512,12 +7512,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>29200</t>
+          <t>29060</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>49201</t>
+          <t>50134</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,55%</t>
         </is>
       </c>
     </row>
@@ -7555,12 +7555,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>20182</t>
+          <t>19238</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>37912</t>
+          <t>37129</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7570,12 +7570,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7590,12 +7590,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>28505</t>
+          <t>27551</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>49284</t>
+          <t>48600</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7605,12 +7605,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7625,12 +7625,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>52786</t>
+          <t>52275</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>77663</t>
+          <t>78657</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7640,12 +7640,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,57%</t>
         </is>
       </c>
     </row>
@@ -7822,7 +7822,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si hacen uso de la sombra para evitar el sol en 2016 (tasa de respuesta: 99,67%)</t>
+          <t>Menores según si el verano pasado hicieron uso de la sombra para evitar el sol en 2016 (tasa de respuesta: 99,67%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8017,12 +8017,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>38151</t>
+          <t>38713</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>56566</t>
+          <t>56310</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8032,12 +8032,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>29,3%</t>
+          <t>29,73%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>43,44%</t>
+          <t>43,25%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>50707</t>
+          <t>50435</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>71684</t>
+          <t>70859</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8067,12 +8067,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>34,42%</t>
+          <t>34,24%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>48,66%</t>
+          <t>48,1%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8087,12 +8087,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>94470</t>
+          <t>95318</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>121627</t>
+          <t>123304</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8102,12 +8102,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>34,04%</t>
+          <t>34,35%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>43,83%</t>
+          <t>44,43%</t>
         </is>
       </c>
     </row>
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>30979</t>
+          <t>29791</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>48293</t>
+          <t>47326</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8145,12 +8145,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>23,79%</t>
+          <t>22,88%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>37,09%</t>
+          <t>36,35%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8165,12 +8165,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>45003</t>
+          <t>45152</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>64882</t>
+          <t>65086</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8180,12 +8180,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>30,55%</t>
+          <t>30,65%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>44,04%</t>
+          <t>44,18%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8200,12 +8200,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>80625</t>
+          <t>80949</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>107224</t>
+          <t>108526</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8215,12 +8215,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>29,05%</t>
+          <t>29,17%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>38,64%</t>
+          <t>39,11%</t>
         </is>
       </c>
     </row>
@@ -8243,12 +8243,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>19417</t>
+          <t>18627</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>34565</t>
+          <t>34898</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8258,12 +8258,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>14,31%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>26,55%</t>
+          <t>26,8%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8278,12 +8278,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>15160</t>
+          <t>14919</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>29480</t>
+          <t>29847</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8293,12 +8293,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>20,01%</t>
+          <t>20,26%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8313,12 +8313,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>38243</t>
+          <t>37790</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>61043</t>
+          <t>59785</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8328,12 +8328,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>21,54%</t>
         </is>
       </c>
     </row>
@@ -8356,12 +8356,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2336</t>
+          <t>2179</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10562</t>
+          <t>10213</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8371,12 +8371,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8391,12 +8391,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1562</t>
+          <t>1571</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9685</t>
+          <t>9024</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8406,12 +8406,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8426,12 +8426,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5113</t>
+          <t>5081</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>15718</t>
+          <t>15831</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,7%</t>
         </is>
       </c>
     </row>
@@ -8469,12 +8469,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>7846</t>
+          <t>7996</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>19139</t>
+          <t>18628</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>14,31%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8504,12 +8504,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2830</t>
+          <t>2797</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>12008</t>
+          <t>11166</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8519,12 +8519,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8539,12 +8539,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>12091</t>
+          <t>12231</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>25755</t>
+          <t>26944</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,71%</t>
         </is>
       </c>
     </row>
@@ -8699,12 +8699,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>89893</t>
+          <t>89914</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>112368</t>
+          <t>111457</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8714,12 +8714,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>43,9%</t>
+          <t>43,91%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>54,87%</t>
+          <t>54,43%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8734,12 +8734,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>82841</t>
+          <t>81894</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>106459</t>
+          <t>106516</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8749,12 +8749,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>37,35%</t>
+          <t>36,92%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>48,0%</t>
+          <t>48,03%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8769,12 +8769,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>178628</t>
+          <t>178883</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>210939</t>
+          <t>210712</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>41,87%</t>
+          <t>41,93%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>49,45%</t>
+          <t>49,4%</t>
         </is>
       </c>
     </row>
@@ -8812,12 +8812,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>48402</t>
+          <t>48291</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>67461</t>
+          <t>69240</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8827,12 +8827,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>23,64%</t>
+          <t>23,58%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>32,94%</t>
+          <t>33,81%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8847,12 +8847,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>67594</t>
+          <t>67599</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>90307</t>
+          <t>89785</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8867,7 +8867,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>40,72%</t>
+          <t>40,48%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8882,12 +8882,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>122094</t>
+          <t>122270</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>151983</t>
+          <t>152471</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>28,62%</t>
+          <t>28,66%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>35,63%</t>
+          <t>35,74%</t>
         </is>
       </c>
     </row>
@@ -8925,12 +8925,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>24564</t>
+          <t>25417</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>41339</t>
+          <t>42183</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8940,12 +8940,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>20,6%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8960,12 +8960,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>25263</t>
+          <t>24563</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>41740</t>
+          <t>41508</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8975,12 +8975,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>53655</t>
+          <t>52493</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>78848</t>
+          <t>77289</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9010,12 +9010,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>18,12%</t>
         </is>
       </c>
     </row>
@@ -9038,12 +9038,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>2511</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10341</t>
+          <t>10228</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9078,7 +9078,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7210</t>
+          <t>6715</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9093,7 +9093,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9108,12 +9108,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3921</t>
+          <t>3836</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>13314</t>
+          <t>13633</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9123,12 +9123,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,2%</t>
         </is>
       </c>
     </row>
@@ -9151,12 +9151,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>4921</t>
+          <t>4431</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>13100</t>
+          <t>13237</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9166,12 +9166,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9186,12 +9186,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>9490</t>
+          <t>9098</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>21526</t>
+          <t>21044</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9221,12 +9221,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>15257</t>
+          <t>16615</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>29925</t>
+          <t>30834</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9236,12 +9236,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>7,23%</t>
         </is>
       </c>
     </row>
@@ -9381,12 +9381,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>57464</t>
+          <t>57270</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>77108</t>
+          <t>76510</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9396,12 +9396,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>37,69%</t>
+          <t>37,57%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>50,58%</t>
+          <t>50,19%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9416,12 +9416,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>51833</t>
+          <t>51781</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>71772</t>
+          <t>71854</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>31,32%</t>
+          <t>31,29%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>43,36%</t>
+          <t>43,41%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9451,12 +9451,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>113640</t>
+          <t>115034</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>142396</t>
+          <t>142106</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9466,12 +9466,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>35,74%</t>
+          <t>36,18%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>44,78%</t>
+          <t>44,69%</t>
         </is>
       </c>
     </row>
@@ -9494,12 +9494,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>54135</t>
+          <t>53476</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>73275</t>
+          <t>72573</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9509,12 +9509,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>35,51%</t>
+          <t>35,08%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>48,06%</t>
+          <t>47,6%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9529,12 +9529,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>69259</t>
+          <t>69871</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>90453</t>
+          <t>91185</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>41,85%</t>
+          <t>42,22%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>54,65%</t>
+          <t>55,09%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9564,12 +9564,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>129081</t>
+          <t>129125</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>158422</t>
+          <t>157641</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9579,12 +9579,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>40,6%</t>
+          <t>40,61%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>49,82%</t>
+          <t>49,58%</t>
         </is>
       </c>
     </row>
@@ -9607,12 +9607,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>11756</t>
+          <t>11947</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>24136</t>
+          <t>25064</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9622,12 +9622,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9642,12 +9642,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>13243</t>
+          <t>13393</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>27130</t>
+          <t>26583</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9657,12 +9657,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>16,06%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>28890</t>
+          <t>28251</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>47781</t>
+          <t>45813</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9692,12 +9692,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>14,41%</t>
         </is>
       </c>
     </row>
@@ -9725,7 +9725,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3204</t>
+          <t>3228</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9740,7 +9740,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9760,7 +9760,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5332</t>
+          <t>5044</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9775,7 +9775,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9790,12 +9790,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>644</t>
+          <t>642</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>5633</t>
+          <t>6348</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9810,7 +9810,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>2,0%</t>
         </is>
       </c>
     </row>
@@ -9833,12 +9833,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2474</t>
+          <t>2194</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>10045</t>
+          <t>8895</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9848,12 +9848,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9868,12 +9868,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>683</t>
+          <t>690</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>6163</t>
+          <t>6412</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9883,12 +9883,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9903,12 +9903,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>4165</t>
+          <t>3644</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>12040</t>
+          <t>12162</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9918,12 +9918,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,83%</t>
         </is>
       </c>
     </row>
@@ -10063,12 +10063,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>84651</t>
+          <t>83457</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>109010</t>
+          <t>107994</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10078,12 +10078,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>41,36%</t>
+          <t>40,78%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>53,27%</t>
+          <t>52,77%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10098,12 +10098,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>80415</t>
+          <t>79366</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>103135</t>
+          <t>102718</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10113,12 +10113,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>39,67%</t>
+          <t>39,15%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>50,88%</t>
+          <t>50,67%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10133,12 +10133,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>171566</t>
+          <t>169712</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>204361</t>
+          <t>204543</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10148,12 +10148,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>42,12%</t>
+          <t>41,66%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>50,17%</t>
+          <t>50,21%</t>
         </is>
       </c>
     </row>
@@ -10176,12 +10176,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>44429</t>
+          <t>44665</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>66138</t>
+          <t>66659</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10191,12 +10191,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>21,71%</t>
+          <t>21,83%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>32,32%</t>
+          <t>32,57%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10211,12 +10211,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>51710</t>
+          <t>52694</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>72971</t>
+          <t>73244</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10226,12 +10226,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>25,51%</t>
+          <t>25,99%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>36,0%</t>
+          <t>36,13%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10246,12 +10246,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>102153</t>
+          <t>102180</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>132196</t>
+          <t>135328</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10266,7 +10266,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>32,45%</t>
+          <t>33,22%</t>
         </is>
       </c>
     </row>
@@ -10289,12 +10289,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>23562</t>
+          <t>22321</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>40773</t>
+          <t>40173</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10304,12 +10304,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>19,92%</t>
+          <t>19,63%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10324,12 +10324,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>21914</t>
+          <t>21893</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>38499</t>
+          <t>37845</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10339,12 +10339,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>18,99%</t>
+          <t>18,67%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10359,12 +10359,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>48903</t>
+          <t>48689</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>72371</t>
+          <t>72533</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10374,12 +10374,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>17,81%</t>
         </is>
       </c>
     </row>
@@ -10402,12 +10402,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2755</t>
+          <t>2774</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>11177</t>
+          <t>11765</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10417,12 +10417,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10437,12 +10437,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2761</t>
+          <t>2726</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>11403</t>
+          <t>11796</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10452,12 +10452,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10472,12 +10472,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>7144</t>
+          <t>7489</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>19365</t>
+          <t>18428</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10487,12 +10487,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,52%</t>
         </is>
       </c>
     </row>
@@ -10515,12 +10515,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>10754</t>
+          <t>10574</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>24475</t>
+          <t>24019</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10530,12 +10530,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10550,12 +10550,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>8345</t>
+          <t>8354</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>20969</t>
+          <t>19832</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10570,7 +10570,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10585,12 +10585,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>21439</t>
+          <t>22386</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>39633</t>
+          <t>39478</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10600,12 +10600,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,69%</t>
         </is>
       </c>
     </row>
@@ -10745,12 +10745,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>289190</t>
+          <t>289028</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>330856</t>
+          <t>331981</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10760,12 +10760,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>41,79%</t>
+          <t>41,76%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>47,81%</t>
+          <t>47,97%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10780,12 +10780,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>284191</t>
+          <t>283558</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>329216</t>
+          <t>330620</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10795,12 +10795,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>38,54%</t>
+          <t>38,46%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>44,65%</t>
+          <t>44,84%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10815,12 +10815,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>589725</t>
+          <t>589881</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>648829</t>
+          <t>652717</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>41,26%</t>
+          <t>41,27%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>45,39%</t>
+          <t>45,66%</t>
         </is>
       </c>
     </row>
@@ -10858,12 +10858,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>195679</t>
+          <t>196518</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>236564</t>
+          <t>235578</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10873,12 +10873,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>28,27%</t>
+          <t>28,39%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>34,18%</t>
+          <t>34,04%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10893,12 +10893,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>253979</t>
+          <t>254779</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>296341</t>
+          <t>298620</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10908,12 +10908,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>34,45%</t>
+          <t>34,55%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>40,19%</t>
+          <t>40,5%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10928,12 +10928,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>460727</t>
+          <t>459659</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>521830</t>
+          <t>520742</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10943,12 +10943,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>32,23%</t>
+          <t>32,16%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>36,51%</t>
+          <t>36,43%</t>
         </is>
       </c>
     </row>
@@ -10971,12 +10971,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>92434</t>
+          <t>92878</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>124332</t>
+          <t>122114</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11006,12 +11006,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>87494</t>
+          <t>87409</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>118798</t>
+          <t>119125</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11021,12 +11021,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11041,12 +11041,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>188678</t>
+          <t>187301</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>232207</t>
+          <t>233160</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11056,12 +11056,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>16,31%</t>
         </is>
       </c>
     </row>
@@ -11084,12 +11084,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>11368</t>
+          <t>11324</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>24936</t>
+          <t>25230</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11104,7 +11104,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11119,12 +11119,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>8387</t>
+          <t>8446</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>21195</t>
+          <t>22100</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11134,12 +11134,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11154,12 +11154,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>23119</t>
+          <t>23177</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>41721</t>
+          <t>41537</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11174,7 +11174,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,91%</t>
         </is>
       </c>
     </row>
@@ -11197,12 +11197,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>31990</t>
+          <t>32089</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>52429</t>
+          <t>53653</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11212,12 +11212,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11232,12 +11232,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>28249</t>
+          <t>28700</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>47858</t>
+          <t>47675</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11247,12 +11247,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11267,12 +11267,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>65192</t>
+          <t>65588</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>93013</t>
+          <t>93371</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11282,12 +11282,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,53%</t>
         </is>
       </c>
     </row>
@@ -11464,7 +11464,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si hacen uso de la sombra para evitar el sol en 2023 (tasa de respuesta: 99,58%)</t>
+          <t>Menores según si el verano pasado hicieron uso de la sombra para evitar el sol en 2023 (tasa de respuesta: 99,58%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -11659,12 +11659,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4554</t>
+          <t>4479</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11181</t>
+          <t>11204</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -11674,12 +11674,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>16,47%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>41,12%</t>
+          <t>41,2%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -11694,12 +11694,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5926</t>
+          <t>5916</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>15620</t>
+          <t>15781</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -11709,12 +11709,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>44,33%</t>
+          <t>44,79%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -11729,12 +11729,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12732</t>
+          <t>12349</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>23761</t>
+          <t>24045</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -11744,12 +11744,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>20,39%</t>
+          <t>19,78%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>38,06%</t>
+          <t>38,52%</t>
         </is>
       </c>
     </row>
@@ -11772,12 +11772,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8440</t>
+          <t>8559</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>16167</t>
+          <t>16185</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -11787,12 +11787,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>31,04%</t>
+          <t>31,47%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>59,45%</t>
+          <t>59,51%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -11807,12 +11807,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9560</t>
+          <t>9454</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>20949</t>
+          <t>20411</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -11822,12 +11822,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>27,13%</t>
+          <t>26,83%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>59,46%</t>
+          <t>57,93%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -11842,12 +11842,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>21099</t>
+          <t>21124</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>34636</t>
+          <t>34490</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -11857,12 +11857,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>33,8%</t>
+          <t>33,84%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>55,48%</t>
+          <t>55,25%</t>
         </is>
       </c>
     </row>
@@ -11885,12 +11885,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3325</t>
+          <t>2952</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9576</t>
+          <t>9235</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -11900,12 +11900,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>35,21%</t>
+          <t>33,96%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11920,12 +11920,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4933</t>
+          <t>4799</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>14153</t>
+          <t>13828</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11935,12 +11935,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>40,17%</t>
+          <t>39,25%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11955,12 +11955,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>10107</t>
+          <t>10105</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>21467</t>
+          <t>21035</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11975,7 +11975,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>34,39%</t>
+          <t>33,7%</t>
         </is>
       </c>
     </row>
@@ -12003,7 +12003,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2931</t>
+          <t>3587</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -12018,7 +12018,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -12073,7 +12073,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3918</t>
+          <t>2950</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -12088,7 +12088,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>4,73%</t>
         </is>
       </c>
     </row>
@@ -12116,7 +12116,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2825</t>
+          <t>3188</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -12131,7 +12131,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -12151,7 +12151,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>4339</t>
+          <t>4464</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -12166,7 +12166,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -12186,7 +12186,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>5421</t>
+          <t>5157</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -12201,7 +12201,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,26%</t>
         </is>
       </c>
     </row>
@@ -12341,12 +12341,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6808</t>
+          <t>6546</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15968</t>
+          <t>15593</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -12356,12 +12356,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>16,65%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>40,62%</t>
+          <t>39,66%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -12376,12 +12376,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9901</t>
+          <t>10001</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>22886</t>
+          <t>22842</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -12391,12 +12391,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,84%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>36,61%</t>
+          <t>36,54%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -12411,12 +12411,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>19359</t>
+          <t>19444</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>35208</t>
+          <t>35189</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -12426,12 +12426,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>19,01%</t>
+          <t>19,09%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>34,57%</t>
+          <t>34,55%</t>
         </is>
       </c>
     </row>
@@ -12454,12 +12454,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>14708</t>
+          <t>14297</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>24716</t>
+          <t>24998</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -12469,12 +12469,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>37,41%</t>
+          <t>36,37%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>62,87%</t>
+          <t>63,59%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -12489,12 +12489,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>31290</t>
+          <t>31782</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>46237</t>
+          <t>46771</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -12504,12 +12504,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>50,05%</t>
+          <t>50,84%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>73,96%</t>
+          <t>74,81%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -12524,12 +12524,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>49435</t>
+          <t>49030</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>68435</t>
+          <t>67813</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -12539,12 +12539,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>48,54%</t>
+          <t>48,15%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>67,2%</t>
+          <t>66,59%</t>
         </is>
       </c>
     </row>
@@ -12567,12 +12567,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3922</t>
+          <t>3556</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>12868</t>
+          <t>12665</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -12582,12 +12582,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>32,73%</t>
+          <t>32,21%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -12602,12 +12602,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3601</t>
+          <t>3203</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>12432</t>
+          <t>12629</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -12617,12 +12617,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>19,88%</t>
+          <t>20,2%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -12637,12 +12637,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>8422</t>
+          <t>9175</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>20690</t>
+          <t>21542</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>21,15%</t>
         </is>
       </c>
     </row>
@@ -12685,7 +12685,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6909</t>
+          <t>6334</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -12700,7 +12700,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>16,11%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -12720,7 +12720,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4213</t>
+          <t>3950</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -12735,7 +12735,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -12755,7 +12755,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6994</t>
+          <t>7615</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -12770,7 +12770,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>7,48%</t>
         </is>
       </c>
     </row>
@@ -13023,12 +13023,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4067</t>
+          <t>4139</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12236</t>
+          <t>12303</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -13038,12 +13038,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>40,49%</t>
+          <t>40,71%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -13058,12 +13058,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5853</t>
+          <t>6047</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>15819</t>
+          <t>16556</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -13073,12 +13073,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>35,8%</t>
+          <t>37,47%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -13093,12 +13093,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>13062</t>
+          <t>12412</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>25576</t>
+          <t>25863</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -13108,12 +13108,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>34,37%</t>
+          <t>34,76%</t>
         </is>
       </c>
     </row>
@@ -13136,12 +13136,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7564</t>
+          <t>7624</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>18356</t>
+          <t>18698</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -13151,12 +13151,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>25,03%</t>
+          <t>25,23%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>60,74%</t>
+          <t>61,87%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -13171,12 +13171,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>13933</t>
+          <t>13961</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>25725</t>
+          <t>25373</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -13186,12 +13186,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>31,53%</t>
+          <t>31,59%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>58,22%</t>
+          <t>57,42%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -13206,12 +13206,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>24404</t>
+          <t>23752</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>40594</t>
+          <t>41006</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -13221,12 +13221,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>32,8%</t>
+          <t>31,92%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>54,55%</t>
+          <t>55,11%</t>
         </is>
       </c>
     </row>
@@ -13249,12 +13249,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4136</t>
+          <t>3905</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>12298</t>
+          <t>11990</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -13264,12 +13264,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>40,69%</t>
+          <t>39,67%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -13284,12 +13284,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>7412</t>
+          <t>7600</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>18853</t>
+          <t>19501</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -13299,12 +13299,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>42,67%</t>
+          <t>44,13%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -13319,12 +13319,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>13629</t>
+          <t>13960</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>27878</t>
+          <t>27243</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -13334,12 +13334,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>18,76%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>37,47%</t>
+          <t>36,61%</t>
         </is>
       </c>
     </row>
@@ -13362,12 +13362,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>682</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6095</t>
+          <t>5827</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -13377,12 +13377,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>20,17%</t>
+          <t>19,28%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -13402,7 +13402,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4653</t>
+          <t>4275</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -13417,7 +13417,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -13432,12 +13432,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>758</t>
+          <t>756</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>7055</t>
+          <t>6828</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -13452,7 +13452,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,18%</t>
         </is>
       </c>
     </row>
@@ -13515,7 +13515,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>4664</t>
+          <t>5202</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -13530,7 +13530,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -13550,7 +13550,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>4488</t>
+          <t>4996</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -13565,7 +13565,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,71%</t>
         </is>
       </c>
     </row>
@@ -13705,12 +13705,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>6398</t>
+          <t>6508</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>17997</t>
+          <t>17112</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -13720,12 +13720,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>14,04%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>38,82%</t>
+          <t>36,91%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -13740,12 +13740,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>9048</t>
+          <t>9408</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>21454</t>
+          <t>21596</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -13755,12 +13755,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>18,88%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>43,06%</t>
+          <t>43,34%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -13775,12 +13775,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>18671</t>
+          <t>18187</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>34909</t>
+          <t>34782</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -13790,12 +13790,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>18,91%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>36,29%</t>
+          <t>36,16%</t>
         </is>
       </c>
     </row>
@@ -13818,12 +13818,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>15896</t>
+          <t>15663</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>27263</t>
+          <t>27251</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -13833,12 +13833,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>34,29%</t>
+          <t>33,78%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>58,8%</t>
+          <t>58,78%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -13853,12 +13853,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>15258</t>
+          <t>14879</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>27568</t>
+          <t>27674</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -13868,12 +13868,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>30,62%</t>
+          <t>29,86%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>55,33%</t>
+          <t>55,54%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -13888,12 +13888,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>33367</t>
+          <t>33960</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>51115</t>
+          <t>51376</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -13903,12 +13903,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>34,69%</t>
+          <t>35,3%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>53,14%</t>
+          <t>53,41%</t>
         </is>
       </c>
     </row>
@@ -13931,12 +13931,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>6372</t>
+          <t>6468</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>15889</t>
+          <t>16032</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13946,12 +13946,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>34,27%</t>
+          <t>34,58%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13966,12 +13966,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>6111</t>
+          <t>6182</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>16944</t>
+          <t>16333</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13981,12 +13981,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>34,0%</t>
+          <t>32,78%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -14001,12 +14001,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>14829</t>
+          <t>15116</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>29069</t>
+          <t>30179</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -14016,12 +14016,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>15,71%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>30,22%</t>
+          <t>31,37%</t>
         </is>
       </c>
     </row>
@@ -14049,7 +14049,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>5344</t>
+          <t>4240</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -14064,7 +14064,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -14084,7 +14084,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>4531</t>
+          <t>4424</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -14099,7 +14099,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -14114,12 +14114,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>677</t>
+          <t>643</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>6320</t>
+          <t>6321</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -14129,7 +14129,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -14157,12 +14157,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>535</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>5528</t>
+          <t>5036</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -14172,12 +14172,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -14197,7 +14197,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>8130</t>
+          <t>7534</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -14212,7 +14212,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>15,12%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -14227,12 +14227,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1497</t>
+          <t>1778</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>11618</t>
+          <t>11413</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -14242,12 +14242,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>11,86%</t>
         </is>
       </c>
     </row>
@@ -14387,12 +14387,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>29311</t>
+          <t>28383</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>46904</t>
+          <t>45672</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -14402,12 +14402,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>20,48%</t>
+          <t>19,84%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>32,78%</t>
+          <t>31,92%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -14422,12 +14422,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>40665</t>
+          <t>40856</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>63416</t>
+          <t>63650</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>21,21%</t>
+          <t>21,3%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>33,07%</t>
+          <t>33,19%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -14457,12 +14457,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>76423</t>
+          <t>74911</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>104199</t>
+          <t>104172</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -14472,12 +14472,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>22,37%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>31,12%</t>
+          <t>31,11%</t>
         </is>
       </c>
     </row>
@@ -14500,12 +14500,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>56193</t>
+          <t>55634</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>76511</t>
+          <t>75672</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -14515,12 +14515,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>39,27%</t>
+          <t>38,88%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>53,47%</t>
+          <t>52,88%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -14535,12 +14535,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>83493</t>
+          <t>81806</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>109368</t>
+          <t>108422</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -14550,12 +14550,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>43,54%</t>
+          <t>42,66%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>57,03%</t>
+          <t>56,54%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -14570,12 +14570,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>145205</t>
+          <t>142664</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>177071</t>
+          <t>180259</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -14585,12 +14585,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>43,36%</t>
+          <t>42,6%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>52,88%</t>
+          <t>53,83%</t>
         </is>
       </c>
     </row>
@@ -14613,12 +14613,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>24907</t>
+          <t>24086</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>41505</t>
+          <t>39754</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -14628,12 +14628,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>29,01%</t>
+          <t>27,78%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -14648,12 +14648,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>29571</t>
+          <t>28943</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>50535</t>
+          <t>49754</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -14663,12 +14663,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>26,35%</t>
+          <t>25,94%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -14683,12 +14683,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>57188</t>
+          <t>58332</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>83553</t>
+          <t>83353</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -14698,12 +14698,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>17,42%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>24,95%</t>
+          <t>24,89%</t>
         </is>
       </c>
     </row>
@@ -14726,12 +14726,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>2749</t>
+          <t>2677</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>11412</t>
+          <t>11769</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -14741,12 +14741,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -14761,12 +14761,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>735</t>
+          <t>734</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>6610</t>
+          <t>6524</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -14781,7 +14781,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -14796,12 +14796,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>4194</t>
+          <t>4181</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>14542</t>
+          <t>14326</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -14816,7 +14816,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,28%</t>
         </is>
       </c>
     </row>
@@ -14839,12 +14839,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>714</t>
+          <t>704</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>6577</t>
+          <t>6946</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -14854,12 +14854,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -14874,12 +14874,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>1460</t>
+          <t>941</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>10400</t>
+          <t>10607</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -14889,12 +14889,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -14909,12 +14909,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>3232</t>
+          <t>3137</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>14581</t>
+          <t>15019</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -14924,12 +14924,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,49%</t>
         </is>
       </c>
     </row>
